--- a/outputs/evaluation/architecture/validation/CF_M06/CF_M06_arch_eval_avg_by_type.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M06/CF_M06_arch_eval_avg_by_type.xlsx
@@ -496,22 +496,22 @@
         <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
     </row>
     <row r="4">
@@ -524,13 +524,13 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>1.3333</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>1.3333</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -580,22 +580,22 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>4.6667</v>
+        <v>5.6667</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>3.6667</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6667</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>3.3333</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6333</v>
+        <v>0.6445</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4286</v>
+        <v>0.5238</v>
       </c>
     </row>
     <row r="7">
@@ -608,22 +608,22 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>7.6667</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>5.3333</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6667</v>
+        <v>2.6667</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>4.6667</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7725</v>
+        <v>0.6631</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6</v>
+        <v>0.5333</v>
       </c>
     </row>
     <row r="8">
@@ -636,13 +636,13 @@
         <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3333</v>
+        <v>0.6667</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3333</v>
+        <v>0.6667</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
@@ -692,22 +692,22 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2.6667</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>2.6667</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0.8889</v>
       </c>
     </row>
   </sheetData>
